--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/BENGALA - 20_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/BENGALA - 20_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BENGALA IRON FAZER250 2012 46634</t>
+          <t>BENGALA/ TUBO IRON FAZER250 2012 46634</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BENGALA IRON CB300 027670</t>
+          <t>BENGALA/ TUBO IRON CB300 027670</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BENGALA IRON BROS NXR150-125 2006 A 2015 009736</t>
+          <t>BENGALA/ TUBO IRON BROS NXR150-125 2006 A 2015 009736</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +492,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BENGALA EXTREMO CG FAN TITAN150 2009 MIX EXT0747</t>
+          <t>BENGALA/ TUBO EXTREMO CG FAN TITAN150 2009 MIX EXT0747</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BENGALA COFAP FAN 2005 A 2018/ CG125 1995 A 2016/ TITAN 1995 A 2004</t>
+          <t>BENGALA/ TUBO COFAP FAN 2005 A 2018/ CG125 1995 A 2016/ TITAN 1995 A 2004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -541,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BENGALA COFAP YBR125 2000 A 2002/ FACTOR125 2009 A 2015/ FAZER150 2014 A 2016</t>
+          <t>BENGALA/ TUBO COFAP YBR125 2000 A 2002/ FACTOR125 2009 A 2015/ FAZER150 2014 A 2016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -562,7 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENGALA COFAP BIZ125 2006 A 2008/ </t>
+          <t xml:space="preserve">BENGALA/ TUBO COFAP BIZ125 2006 A 2008/ </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -583,7 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +584,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BENGALA GP7 CROSSER XTZ150 1211929</t>
+          <t>BENGALA/ TUBO GP7 CROSSER XTZ150 1211929</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +592,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +604,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BENGALA GP7 FAN TITAN CG150 1101971</t>
+          <t>BENGALA/ TUBO GP7 FAN TITAN CG150 1101971</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -625,7 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +624,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BENGALA RENTEC CG TODAY/ TITAN 1999 A 2004/ FAN 2008</t>
+          <t>BENGALA/ TUBO RENTEC CG TODAY/ TITAN 1999 A 2004/ FAN 2008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +632,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -659,17 +644,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BENGALA RENTEC TITAN150 2004 A 2008/ FAN 2009 MIX</t>
+          <t>BENGALA/ TUBO RENTEC TITAN150 2004 A 2008/ FAN 2009 MIX</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
     </row>
@@ -684,7 +664,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BENGALA MHX BIZ100 2005/ POP100 2007/ POP110I 2016</t>
+          <t>BENGALA/ TUBO MHX BIZ100 2005/ POP100 2007/ POP110I 2016</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -692,7 +672,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -705,7 +684,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BENGALA KATANA XRE300</t>
+          <t>BENGALA/ TUBO KATANA XRE300</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -713,7 +692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -726,7 +704,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BENGALA MHX CG TITAN FAN125 KS ES</t>
+          <t>BENGALA/ TUBO MHX CG TITAN FAN125 KS ES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -734,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -747,7 +724,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BENGALA BRAVIC FAN TITAN160 2018 BMA36020</t>
+          <t>BENGALA/ TUBO BRAVIC FAN TITAN160 2018 BMA36020</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -755,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -768,7 +744,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENGALA SMARTFOX TWISTER CBX250 2001 A 2008/ CB300 2009 A 2015</t>
+          <t>BENGALA/ TUBO SMARTFOX TWISTER CBX250 2001 A 2008/ CB300 2009 A 2015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -776,7 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -789,7 +764,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CILINDRO EXTERNO IRON FAN CG125 KS 2009 005197</t>
+          <t>BENGALA/ TUBO  EXTERNO IRON FAN CG125 KS 2009 005197</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -797,7 +772,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -810,7 +784,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CILINDRO EXTERNO FAN CG125 2016 A 2018 196176</t>
+          <t>BENGALA/ TUBO EXTERNO FAN CG125 2016 A 2018 196176</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -818,7 +792,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -831,7 +804,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CILINDRO EXTERNO IRON FAN TITAN160 2016 A 2017 196174</t>
+          <t>BENGALA/ TUBO EXTERNO IRON FAN TITAN160 2016 A 2017 196174</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -839,7 +812,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
